--- a/Unmapped_TCINs_with_recommendations.xlsx
+++ b/Unmapped_TCINs_with_recommendations.xlsx
@@ -107,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -129,11 +129,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -188,6 +232,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -702,9 +748,9 @@
           <t>Sanitizing</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>DECISION NEEDED</t>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Decided</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -714,7 +760,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>COLLISION: in the locked CASE, the product_title LIKE '%Holiday%' branch sits ABOVE the %WIP-SAN-% branch. Run as-is against this Target description and you get Other / Holiday &amp; Seasonal, not Sanitizing. 102,672 units - 25% of this set - turns on the call. See 'Judgment Calls'.</t>
+          <t>DECIDED 2026-09-14: load as Personal Care / Sanitizing, overriding the CASE. COLLISION being overridden: in the locked CASE the product_title LIKE '%Holiday%' branch sits ABOVE the %WIP-SAN-% branch, so run as-is against this Target description it returns Other / Holiday &amp; Seasonal. 102,672 units - 25% of this set - turned on the call. See 'Judgment Calls'.</t>
         </is>
       </c>
     </row>
@@ -1272,22 +1318,22 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Bundles &amp; Kits</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>DECISION NEEDED</t>
+          <t>Flushable</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Decided</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Closest precedent is the Shopify twin of this exact construction - K-DIS-WHI-FLU-FRA 'Flushable Wipes Starter Kit - Biom Home Dispenser' - which is Personal Care / Bundles &amp; Kits.</t>
+          <t>Mirrors the baby treatment: K-DIS-2BAB-WHI, -LGR and -PUR are all Personal Care / Baby - classified by wipe type, not by kit-ness (verified in dim_product, is_current, 2026-09-14). The Shopify twin K-DIS-WHI-FLU-FRA 'Flushable Wipes Starter Kit' sits in Personal Care / Bundles &amp; Kits; that reading was considered and not taken, so the flushable franchise stays in one sub-category.</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>COLLISION: the locked CASE matches this on K-%DIS-%FLU-% and returns Other / Bundles &amp; Kits, parking 35,496 units of flushable wipes under Other. The baby equivalent (K-DIS-2BAB-WHI) only escapes that because of an explicit carve-out branch; flushable has none. See 'Judgment Calls'.</t>
+          <t>DECIDED 2026-09-14: load as Personal Care / Flushable, overriding the CASE. COLLISION being overridden: the locked CASE matches this on K-%DIS-%FLU-% and returns Other / Bundles &amp; Kits, parking 35,496 units of flushable wipes under Other. The baby equivalent escapes only through an explicit carve-out branch; flushable has none. See 'Judgment Calls'.</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1351,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Highlighted rows need a human call before loading - see the 'Judgment Calls' tab. Every other row is what the locked SKU-pattern taxonomy in canvas_delta.py returns for that manufacturer style, confirmed against an existing product already carrying that category.</t>
+          <t>Both highlighted rows were settled by a human call on 2026-09-14 - see the 'Judgment Calls' tab for what was decided and why. Every other row is what the locked SKU-pattern taxonomy in canvas_delta.py returns for that manufacturer style, confirmed against an existing product already carrying that category. Ready to load.</t>
         </is>
       </c>
     </row>
@@ -1405,11 +1451,11 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Rows needing a human call</t>
+          <t>Rows settled by a human call (see Judgment Calls)</t>
         </is>
       </c>
       <c r="B8" s="13">
-        <f>COUNTIF('Unmapped TCINs'!K2:K11,"DECISION NEEDED")</f>
+        <f>COUNTIF('Unmapped TCINs'!K2:K11,"Decided")</f>
         <v/>
       </c>
     </row>
@@ -1421,7 +1467,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Load the recommended category/sub-category below; settle the 2 flagged rows first</t>
+          <t>Ready to load - take the category/sub-category below as-is; both flagged rows were settled 2026-09-14.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1672,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Parent category rollup: Personal Care takes 6 of the 10 items, Cleaning 4. Both flagged rows sit in Personal Care under the recommendation; the locked logic as written would move both to Other, which is what makes them worth settling deliberately.</t>
+          <t>Parent category rollup: Personal Care takes 6 of the 10 items, Cleaning 4. Both settled rows sit in Personal Care - Sanitizing and Flushable respectively - where the locked logic as written would have moved both to Other. Personal Care / Bundles &amp; Kits reads zero because the flushable kit was settled as Flushable instead; the row is kept so the option stays visible.</t>
         </is>
       </c>
     </row>
@@ -1656,14 +1702,14 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Two rows need a human call before loading</t>
+          <t>Two rows needed a human call - both settled 2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Both are cases where the locked SKU-pattern CASE in canvas_delta.py returns a category that is defensible as code but wrong as merchandising. Applying the logic blindly moves 138,168 units - 34% of this set - into 'Other'.</t>
+          <t>Both were cases where the locked SKU-pattern CASE in canvas_delta.py returns a category that is defensible as code but wrong as merchandising. Applying the logic blindly would have moved 138,168 units - 34% of this set - into 'Other'. Both decisions keep those units in Personal Care.</t>
         </is>
       </c>
     </row>
@@ -1674,8 +1720,8 @@
           <t>1011278742 - Sanitizing Go-Pack Holiday Bergamot Bloom, 20ct (102,672 units)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="26" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="31" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
@@ -1697,7 +1743,7 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>RECOMMENDED</t>
+          <t>DECIDED 2026-09-14</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1707,7 +1753,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>This is a standard 20ct sanitizing hand-wipe go-pack in a seasonal scent, not a seasonal gift item. Its dept/class twin P-20WIP-SAN-STL-TRV is Personal Care / Sanitizing, and the BER scent is already Sanitizing on CSP-WIP-SAN-BER-TRV-40. Every existing Holiday &amp; Seasonal row is a K-HOL- gifting bundle, which this is not.</t>
+          <t>This is a standard 20ct sanitizing hand-wipe go-pack in a seasonal scent, not a seasonal gift item. Its dept/class twin P-20WIP-SAN-STL-TRV is Personal Care / Sanitizing, and the BER scent is already Sanitizing on CSP-WIP-SAN-BER-TRV-40. All four current Holiday &amp; Seasonal rows are gifting bundles carrying no manufacturer style at all ('The Holiday Bundle', 'Holiday Collection - Gifting Suite'), which this is not. Verified in dim_product, is_current, 2026-09-14.</t>
         </is>
       </c>
     </row>
@@ -1751,8 +1797,8 @@
           <t>95285662 - White Flushable One Handed Kit, 120ct (35,496 units)</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="26" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="31" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
@@ -1774,34 +1820,34 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>RECOMMENDED</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+          <t>Considered, not taken</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal Care / Bundles &amp; Kits</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Matches the Shopify twin of the identical construction - K-DIS-WHI-FLU-FRA 'Flushable Wipes Starter Kit - Biom Home Dispenser' - which is Personal Care / Bundles &amp; Kits. Keeps the dispenser-plus-wipes entry SKU visible as a kit while holding the units in Personal Care.</t>
+          <t>Matches the Shopify twin of the identical construction - K-DIS-WHI-FLU-FRA 'Flushable Wipes Starter Kit - Biom Home Dispenser' - which is Personal Care / Bundles &amp; Kits. Not taken: it splits the flushable franchise across two sub-categories, and dept/class 253-6 is easier to read as one form.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Alternative</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+          <t>DECIDED 2026-09-14</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Personal Care / Flushable</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Mirrors the baby treatment - K-DIS-2BAB-WHI is Personal Care / Baby, classified by wipe type rather than by kit-ness. Pick this if you want all of dept/class 253-6 to read as one form in sell-through.</t>
+          <t>Mirrors the baby treatment: K-DIS-2BAB-WHI, -LGR and -PUR all resolve to Personal Care / Baby - classified by wipe type rather than by kit-ness (verified in dim_product, is_current, 2026-09-14). All of dept/class 253-6 therefore reads as one form in sell-through.</t>
         </is>
       </c>
     </row>
